--- a/output/2026-09-19_18_Croazia_Osječko-baranjska_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-19_18_Croazia_Osječko-baranjska_Componentistica_Ventilazione_industriale.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,6 @@
           <t>031/275-273</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Distributore elektromaterijal/rasvjeta verificato, con linea prodotti ventilatori a marchio Aspira (ventilatori ugradni/kupaonski, serie Simplex/Evolution/Velo) confermata a catalogo. Linea prevalentemente residenziale/bagno, non strettamente industriale pesante; email generica non trovata.</t>
@@ -616,7 +615,6 @@
           <t>031 252 224</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Catena tecnica verificata (sito ufficiale, store locator) con categoria dedicata 'Industrijski ventilatori' (es. Terma Air FT-500ST, FT-600PP), oltre a ventilatori da ambiente e recuperatori. Numero di filiale non riconfermato da fonte indipendente; email generica non trovata.</t>
@@ -624,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-19_18_Croazia_Osječko-baranjska_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-19_18_Croazia_Osječko-baranjska_Componentistica_Ventilazione_industriale.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Catena tecnica verificata (sito ufficiale, store locator) con categoria dedicata 'Industrijski ventilatori' (es. Terma Air FT-500ST, FT-600PP), oltre a ventilatori da ambiente e recuperatori. Numero di filiale non riconfermato da fonte indipendente; email generica non trovata.</t>
+          <t>Catena tecnica verificata (sito ufficiale, store locator) con categoria dedicata 'Industrijski ventilatori' (es. Terma Air FT-500ST, FT-600PP), oltre a ventilatori da ambiente e recuperatori. Numero di filiale non riconfermato da fonte indipendente; email generica non trovata. [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
